--- a/Wholesale_Today_Workflow_20260620.xlsx
+++ b/Wholesale_Today_Workflow_20260620.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>RESEARCH BLOCKED — try McDowell Homes / Marcus Ezzone 440-577-6590 (neighbor 4150, UNVERIFIED); else pull from Redfin</t>
+          <t>Pete Cymbal · TimberVine/eXp · pete.cymbal@timbervinegroup.com · 216-353-4120 — DRAFT STAGED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
